--- a/Aktiviteetit/Vuosi_2025/Aktiviteetit_Elokuu.xlsx
+++ b/Aktiviteetit/Vuosi_2025/Aktiviteetit_Elokuu.xlsx
@@ -1,37 +1,237 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Teppo\projektit\running_stat\Aktiviteetit\Vuosi_2025\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D1E875-BD9C-4C23-B2B8-1BAFA9CD9255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="activities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="activities" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Distance (km)</t>
+  </si>
+  <si>
+    <t>Moving Time (h:min)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Average Speed (min/km)</t>
+  </si>
+  <si>
+    <t>Average Speed (m/s)</t>
+  </si>
+  <si>
+    <t>Average Heart rate (b/min)</t>
+  </si>
+  <si>
+    <t>Afternoon Run</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>2025-08-30T15:17:32</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>Tempo 5K</t>
+  </si>
+  <si>
+    <t>2025-08-30T13:56:56</t>
+  </si>
+  <si>
+    <t>04:11</t>
+  </si>
+  <si>
+    <t>2025-08-29T17:37:22</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>Night Run</t>
+  </si>
+  <si>
+    <t>2025-08-26T21:17:00</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>Lunch Run</t>
+  </si>
+  <si>
+    <t>2025-08-24T11:07:59</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>Morning Run</t>
+  </si>
+  <si>
+    <t>2025-08-23T10:24:35</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>Tempo 8K</t>
+  </si>
+  <si>
+    <t>2025-08-21T19:06:34</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>2025-08-20T12:10:06</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>2025-08-19T13:36:01</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>2025-08-17T15:52:00</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>2025-08-16T13:54:23</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>2025-08-15T16:14:51</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>Tempo 10K</t>
+  </si>
+  <si>
+    <t>2025-08-14T18:51:31</t>
+  </si>
+  <si>
+    <t>04:19</t>
+  </si>
+  <si>
+    <t>Evening Run</t>
+  </si>
+  <si>
+    <t>2025-08-13T18:22:47</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>2025-08-12T21:21:57</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>2025-08-10T18:58:38</t>
+  </si>
+  <si>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>2025-08-09T19:30:35</t>
+  </si>
+  <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>2025-08-07T17:33:41</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>Tempo 12K Altpace</t>
+  </si>
+  <si>
+    <t>2025-08-06T09:56:58</t>
+  </si>
+  <si>
+    <t>2025-08-05T11:49:37</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>2025-08-04T22:22:25</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>2025-08-03T09:53:19</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>2025-08-02T10:20:49</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +246,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normaali" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,189 +570,631 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance (km)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Moving Time (h:min)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Average Speed (min/km)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Average Speed (m/s)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Average Heart rate (b/min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lunch Run</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1.75</v>
+      </c>
+      <c r="C2">
+        <v>532</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>3.2959999999999998</v>
+      </c>
+      <c r="H2">
+        <v>152.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>5.18</v>
+      </c>
+      <c r="C3">
+        <v>1304</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>3.9740000000000002</v>
+      </c>
+      <c r="H3">
+        <v>169.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>10.061</v>
+      </c>
+      <c r="C4">
+        <v>3471</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>2.8980000000000001</v>
+      </c>
+      <c r="H4">
+        <v>140.19999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>5.44</v>
+      </c>
+      <c r="C5">
+        <v>2434</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>2.2330000000000001</v>
+      </c>
+      <c r="H5">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>18.45</v>
+      </c>
+      <c r="C6">
+        <v>6099</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="H6">
+        <v>143.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C7">
+        <v>2918</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7">
+        <v>2.8090000000000002</v>
+      </c>
+      <c r="H7">
+        <v>141.19999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>8.08</v>
+      </c>
+      <c r="C8">
+        <v>2135</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>3.7869999999999999</v>
+      </c>
+      <c r="H8">
+        <v>160.69999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>10.57</v>
+      </c>
+      <c r="C9">
+        <v>3603</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>2.9340000000000002</v>
+      </c>
+      <c r="H9">
+        <v>140.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>12.01</v>
+      </c>
+      <c r="C10">
+        <v>4198</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10">
+        <v>2.8610000000000002</v>
+      </c>
+      <c r="H10">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>22.33</v>
+      </c>
+      <c r="C11">
+        <v>6595</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="H11">
+        <v>159.19999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>10.17</v>
+      </c>
+      <c r="C12">
+        <v>3736</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12">
+        <v>2.7229999999999999</v>
+      </c>
+      <c r="H12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>10.32</v>
+      </c>
+      <c r="C13">
+        <v>3640</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13">
+        <v>2.835</v>
+      </c>
+      <c r="H13">
+        <v>142.80000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14">
+        <v>10.01</v>
+      </c>
+      <c r="C14">
+        <v>2602</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14">
+        <v>3.8479999999999999</v>
+      </c>
+      <c r="H14">
+        <v>166.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="C15">
+        <v>6303</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15">
+        <v>2.8719999999999999</v>
+      </c>
+      <c r="H15">
+        <v>140.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="C16">
+        <v>3762</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16">
+        <v>2.14</v>
+      </c>
+      <c r="H16">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17">
+        <v>21.19</v>
+      </c>
+      <c r="C17">
+        <v>6771</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>3.129</v>
+      </c>
+      <c r="H17">
+        <v>149.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <v>10.38</v>
+      </c>
+      <c r="C18">
+        <v>4086</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>2.5409999999999999</v>
+      </c>
+      <c r="H18">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>12.54</v>
+      </c>
+      <c r="C19">
+        <v>4822</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19">
+        <v>2.601</v>
+      </c>
+      <c r="H19">
+        <v>129.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20">
+        <v>12.03</v>
+      </c>
+      <c r="C20">
+        <v>3185</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20">
+        <v>3.778</v>
+      </c>
+      <c r="H20">
+        <v>164.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>12.46</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C21">
         <v>4642</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-08-05T11:49:37</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06:12</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>2.684</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21">
+        <v>2.6840000000000002</v>
+      </c>
+      <c r="H21">
         <v>141</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Night Run</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C3" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C22">
         <v>1933</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025-08-04T22:22:25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2.119</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>2.1190000000000002</v>
+      </c>
+      <c r="H22">
         <v>116.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Morning Run</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
         <v>22.12</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C23">
         <v>7477</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2025-08-03T09:53:19</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>05:38</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2.958</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>2.9580000000000002</v>
+      </c>
+      <c r="H23">
         <v>150</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Morning Run</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>10.06</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C24">
         <v>3734</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-08-02T10:20:49</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>06:11</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24">
         <v>2.694</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H24">
         <v>142.5</v>
       </c>
     </row>
